--- a/artfynd/A 39496-2024 artfynd.xlsx
+++ b/artfynd/A 39496-2024 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120064431</v>
+        <v>120062610</v>
       </c>
       <c r="B3" t="n">
-        <v>91840</v>
+        <v>78263</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,41 +799,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503138</v>
+        <v>503313</v>
       </c>
       <c r="R3" t="n">
-        <v>6919076</v>
+        <v>6918866</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,12 +887,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120062610</v>
+        <v>120064431</v>
       </c>
       <c r="B5" t="n">
-        <v>78263</v>
+        <v>91840</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,41 +1023,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503313</v>
+        <v>503138</v>
       </c>
       <c r="R5" t="n">
-        <v>6918866</v>
+        <v>6919076</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,12 +1111,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 39496-2024 artfynd.xlsx
+++ b/artfynd/A 39496-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120064032</v>
+        <v>120064366</v>
       </c>
       <c r="B2" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>503163</v>
+        <v>503147</v>
       </c>
       <c r="R2" t="n">
-        <v>6919011</v>
+        <v>6919083</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120062610</v>
+        <v>120064397</v>
       </c>
       <c r="B3" t="n">
-        <v>78263</v>
+        <v>97907</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,38 +799,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503313</v>
+        <v>503150</v>
       </c>
       <c r="R3" t="n">
-        <v>6918866</v>
+        <v>6919090</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -862,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120064680</v>
+        <v>120063854</v>
       </c>
       <c r="B4" t="n">
-        <v>95455</v>
+        <v>97907</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,41 +920,50 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503081</v>
+        <v>503171</v>
       </c>
       <c r="R4" t="n">
-        <v>6919157</v>
+        <v>6918993</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +1002,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,22 +1017,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120064431</v>
+        <v>120064738</v>
       </c>
       <c r="B5" t="n">
-        <v>91840</v>
+        <v>79643</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,37 +1045,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6464</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503138</v>
+        <v>503079</v>
       </c>
       <c r="R5" t="n">
-        <v>6919076</v>
+        <v>6919159</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1114,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,22 +1129,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120062695</v>
+        <v>120063290</v>
       </c>
       <c r="B6" t="n">
-        <v>97907</v>
+        <v>90527</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,42 +1153,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503271</v>
+        <v>503218</v>
       </c>
       <c r="R6" t="n">
-        <v>6918864</v>
+        <v>6918907</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1239,10 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120063751</v>
+        <v>120062713</v>
       </c>
       <c r="B7" t="n">
-        <v>97907</v>
+        <v>57326</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,47 +1265,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>503174</v>
+        <v>503279</v>
       </c>
       <c r="R7" t="n">
-        <v>6918958</v>
+        <v>6918859</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1360,7 +1370,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120063873</v>
+        <v>120064032</v>
       </c>
       <c r="B8" t="n">
         <v>97907</v>
@@ -1393,29 +1403,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>503181</v>
+        <v>503163</v>
       </c>
       <c r="R8" t="n">
-        <v>6918946</v>
+        <v>6919011</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1444,7 +1445,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1454,7 +1455,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,22 +1470,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120062915</v>
+        <v>120063353</v>
       </c>
       <c r="B9" t="n">
-        <v>91852</v>
+        <v>78263</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1493,38 +1494,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4366</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>503303</v>
+        <v>503182</v>
       </c>
       <c r="R9" t="n">
-        <v>6918868</v>
+        <v>6918921</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1593,10 +1594,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120063666</v>
+        <v>120062695</v>
       </c>
       <c r="B10" t="n">
-        <v>79115</v>
+        <v>97907</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1605,41 +1606,45 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>503181</v>
+        <v>503271</v>
       </c>
       <c r="R10" t="n">
-        <v>6918937</v>
+        <v>6918864</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1668,7 +1673,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1678,7 +1683,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,22 +1698,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120063353</v>
+        <v>120064743</v>
       </c>
       <c r="B11" t="n">
-        <v>78263</v>
+        <v>97907</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1717,38 +1722,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>503182</v>
+        <v>503071</v>
       </c>
       <c r="R11" t="n">
-        <v>6918921</v>
+        <v>6919178</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1817,7 +1831,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120064397</v>
+        <v>120063873</v>
       </c>
       <c r="B12" t="n">
         <v>97907</v>
@@ -1852,7 +1866,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1866,10 +1880,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>503150</v>
+        <v>503181</v>
       </c>
       <c r="R12" t="n">
-        <v>6919090</v>
+        <v>6918946</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1901,7 +1915,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1911,7 +1925,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1938,10 +1952,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120064738</v>
+        <v>120063775</v>
       </c>
       <c r="B13" t="n">
-        <v>79643</v>
+        <v>91840</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1954,37 +1968,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6464</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>503079</v>
+        <v>503180</v>
       </c>
       <c r="R13" t="n">
-        <v>6919159</v>
+        <v>6918964</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2013,7 +2027,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2023,7 +2037,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2038,19 +2052,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120063854</v>
+        <v>120063751</v>
       </c>
       <c r="B14" t="n">
         <v>97907</v>
@@ -2085,7 +2099,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2099,10 +2113,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>503171</v>
+        <v>503174</v>
       </c>
       <c r="R14" t="n">
-        <v>6918993</v>
+        <v>6918958</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2171,10 +2185,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120063775</v>
+        <v>120064281</v>
       </c>
       <c r="B15" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2183,38 +2197,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>503180</v>
+        <v>503147</v>
       </c>
       <c r="R15" t="n">
-        <v>6918964</v>
+        <v>6919079</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2283,10 +2306,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120064743</v>
+        <v>120062610</v>
       </c>
       <c r="B16" t="n">
-        <v>97907</v>
+        <v>78263</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2295,50 +2318,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>503071</v>
+        <v>503313</v>
       </c>
       <c r="R16" t="n">
-        <v>6919178</v>
+        <v>6918866</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2367,7 +2381,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2377,7 +2391,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2392,22 +2406,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120063290</v>
+        <v>120064120</v>
       </c>
       <c r="B17" t="n">
-        <v>90527</v>
+        <v>97907</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2416,41 +2430,50 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>503218</v>
+        <v>503169</v>
       </c>
       <c r="R17" t="n">
-        <v>6918907</v>
+        <v>6919008</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2479,7 +2502,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2489,7 +2512,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2504,12 +2527,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2628,7 +2651,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120064281</v>
+        <v>120064457</v>
       </c>
       <c r="B19" t="n">
         <v>97907</v>
@@ -2661,26 +2684,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>503147</v>
+        <v>503135</v>
       </c>
       <c r="R19" t="n">
-        <v>6919079</v>
+        <v>6919127</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2749,10 +2763,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120062713</v>
+        <v>120064431</v>
       </c>
       <c r="B20" t="n">
-        <v>57326</v>
+        <v>91840</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2761,43 +2775,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>503279</v>
+        <v>503138</v>
       </c>
       <c r="R20" t="n">
-        <v>6918859</v>
+        <v>6919076</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2866,10 +2875,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120064120</v>
+        <v>120064680</v>
       </c>
       <c r="B21" t="n">
-        <v>97907</v>
+        <v>95455</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2878,47 +2887,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>503169</v>
+        <v>503081</v>
       </c>
       <c r="R21" t="n">
-        <v>6919008</v>
+        <v>6919157</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2987,10 +2987,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120064366</v>
+        <v>120062915</v>
       </c>
       <c r="B22" t="n">
-        <v>79607</v>
+        <v>91852</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2999,25 +2999,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>4366</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3027,13 +3027,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503147</v>
+        <v>503303</v>
       </c>
       <c r="R22" t="n">
-        <v>6919083</v>
+        <v>6918868</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3087,22 +3087,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120064457</v>
+        <v>120063666</v>
       </c>
       <c r="B23" t="n">
-        <v>97907</v>
+        <v>79115</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3111,41 +3111,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>503135</v>
+        <v>503181</v>
       </c>
       <c r="R23" t="n">
-        <v>6919127</v>
+        <v>6918937</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3199,12 +3199,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 39496-2024 artfynd.xlsx
+++ b/artfynd/A 39496-2024 artfynd.xlsx
@@ -1253,10 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120062713</v>
+        <v>120064032</v>
       </c>
       <c r="B7" t="n">
-        <v>57326</v>
+        <v>97907</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,43 +1265,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>503279</v>
+        <v>503163</v>
       </c>
       <c r="R7" t="n">
-        <v>6918859</v>
+        <v>6919011</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1370,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120064032</v>
+        <v>120062713</v>
       </c>
       <c r="B8" t="n">
-        <v>97907</v>
+        <v>57326</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1382,38 +1377,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>503163</v>
+        <v>503279</v>
       </c>
       <c r="R8" t="n">
-        <v>6919011</v>
+        <v>6918859</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1710,10 +1710,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120064743</v>
+        <v>120063775</v>
       </c>
       <c r="B11" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1722,47 +1722,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>503071</v>
+        <v>503180</v>
       </c>
       <c r="R11" t="n">
-        <v>6919178</v>
+        <v>6918964</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1831,7 +1822,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120063873</v>
+        <v>120064743</v>
       </c>
       <c r="B12" t="n">
         <v>97907</v>
@@ -1866,7 +1857,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1876,17 +1867,17 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>503181</v>
+        <v>503071</v>
       </c>
       <c r="R12" t="n">
-        <v>6918946</v>
+        <v>6919178</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1915,7 +1906,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1925,7 +1916,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1940,22 +1931,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120063775</v>
+        <v>120063873</v>
       </c>
       <c r="B13" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1964,41 +1955,50 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>503180</v>
+        <v>503181</v>
       </c>
       <c r="R13" t="n">
-        <v>6918964</v>
+        <v>6918946</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2052,12 +2052,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2539,10 +2539,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120063670</v>
+        <v>120064457</v>
       </c>
       <c r="B18" t="n">
-        <v>78263</v>
+        <v>97907</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2551,41 +2551,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>503181</v>
+        <v>503135</v>
       </c>
       <c r="R18" t="n">
-        <v>6918937</v>
+        <v>6919127</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2639,22 +2639,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120064457</v>
+        <v>120063670</v>
       </c>
       <c r="B19" t="n">
-        <v>97907</v>
+        <v>78263</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2663,41 +2663,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>503135</v>
+        <v>503181</v>
       </c>
       <c r="R19" t="n">
-        <v>6919127</v>
+        <v>6918937</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2751,12 +2751,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 39496-2024 artfynd.xlsx
+++ b/artfynd/A 39496-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120064366</v>
+        <v>120062695</v>
       </c>
       <c r="B2" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>503147</v>
+        <v>503271</v>
       </c>
       <c r="R2" t="n">
-        <v>6919083</v>
+        <v>6918864</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,19 +779,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120064397</v>
+        <v>120064120</v>
       </c>
       <c r="B3" t="n">
         <v>97907</v>
@@ -822,7 +826,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -836,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503150</v>
+        <v>503169</v>
       </c>
       <c r="R3" t="n">
-        <v>6919090</v>
+        <v>6919008</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -871,7 +875,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +885,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,7 +912,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120063854</v>
+        <v>120063873</v>
       </c>
       <c r="B4" t="n">
         <v>97907</v>
@@ -943,7 +947,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -953,17 +957,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503171</v>
+        <v>503181</v>
       </c>
       <c r="R4" t="n">
-        <v>6918993</v>
+        <v>6918946</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,7 +996,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +1006,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,22 +1021,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120064738</v>
+        <v>120063670</v>
       </c>
       <c r="B5" t="n">
-        <v>79643</v>
+        <v>78263</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,25 +1045,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1069,10 +1073,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503079</v>
+        <v>503181</v>
       </c>
       <c r="R5" t="n">
-        <v>6919159</v>
+        <v>6918937</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1104,7 +1108,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,7 +1118,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,10 +1145,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120063290</v>
+        <v>120064457</v>
       </c>
       <c r="B6" t="n">
-        <v>90527</v>
+        <v>97907</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1153,38 +1157,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503218</v>
+        <v>503135</v>
       </c>
       <c r="R6" t="n">
-        <v>6918907</v>
+        <v>6919127</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1253,7 +1257,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120064032</v>
+        <v>120064397</v>
       </c>
       <c r="B7" t="n">
         <v>97907</v>
@@ -1286,20 +1290,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>503163</v>
+        <v>503150</v>
       </c>
       <c r="R7" t="n">
-        <v>6919011</v>
+        <v>6919090</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1328,7 +1341,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1338,7 +1351,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1353,22 +1366,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120062713</v>
+        <v>120063854</v>
       </c>
       <c r="B8" t="n">
-        <v>57326</v>
+        <v>97907</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,43 +1390,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>503279</v>
+        <v>503171</v>
       </c>
       <c r="R8" t="n">
-        <v>6918859</v>
+        <v>6918993</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1594,10 +1611,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120062695</v>
+        <v>120064738</v>
       </c>
       <c r="B10" t="n">
-        <v>97907</v>
+        <v>79643</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1606,45 +1623,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>503271</v>
+        <v>503079</v>
       </c>
       <c r="R10" t="n">
-        <v>6918864</v>
+        <v>6919159</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1673,7 +1686,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1683,7 +1696,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1698,22 +1711,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120063775</v>
+        <v>120063666</v>
       </c>
       <c r="B11" t="n">
-        <v>91840</v>
+        <v>79115</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1722,41 +1735,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>503180</v>
+        <v>503181</v>
       </c>
       <c r="R11" t="n">
-        <v>6918964</v>
+        <v>6918937</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1785,7 +1798,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1795,7 +1808,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1810,19 +1823,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120064743</v>
+        <v>120063751</v>
       </c>
       <c r="B12" t="n">
         <v>97907</v>
@@ -1857,7 +1870,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1871,10 +1884,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>503071</v>
+        <v>503174</v>
       </c>
       <c r="R12" t="n">
-        <v>6919178</v>
+        <v>6918958</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1943,10 +1956,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120063873</v>
+        <v>120062713</v>
       </c>
       <c r="B13" t="n">
-        <v>97907</v>
+        <v>57326</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1955,35 +1968,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1992,13 +2001,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>503181</v>
+        <v>503279</v>
       </c>
       <c r="R13" t="n">
-        <v>6918946</v>
+        <v>6918859</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2027,7 +2036,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2037,7 +2046,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2052,22 +2061,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120063751</v>
+        <v>120063290</v>
       </c>
       <c r="B14" t="n">
-        <v>97907</v>
+        <v>90527</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2076,47 +2085,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>503174</v>
+        <v>503218</v>
       </c>
       <c r="R14" t="n">
-        <v>6918958</v>
+        <v>6918907</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2185,10 +2185,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120064281</v>
+        <v>120064366</v>
       </c>
       <c r="B15" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2197,50 +2197,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
         <v>503147</v>
       </c>
       <c r="R15" t="n">
-        <v>6919079</v>
+        <v>6919083</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2269,7 +2260,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2279,7 +2270,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2294,22 +2285,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120062610</v>
+        <v>120064032</v>
       </c>
       <c r="B16" t="n">
-        <v>78263</v>
+        <v>97907</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2318,41 +2309,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>503313</v>
+        <v>503163</v>
       </c>
       <c r="R16" t="n">
-        <v>6918866</v>
+        <v>6919011</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2381,7 +2372,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2391,7 +2382,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2406,22 +2397,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120064120</v>
+        <v>120062915</v>
       </c>
       <c r="B17" t="n">
-        <v>97907</v>
+        <v>91852</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2430,50 +2421,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>503169</v>
+        <v>503303</v>
       </c>
       <c r="R17" t="n">
-        <v>6919008</v>
+        <v>6918868</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2502,7 +2484,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2512,7 +2494,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2527,22 +2509,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120064457</v>
+        <v>120062610</v>
       </c>
       <c r="B18" t="n">
-        <v>97907</v>
+        <v>78263</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2551,41 +2533,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>503135</v>
+        <v>503313</v>
       </c>
       <c r="R18" t="n">
-        <v>6919127</v>
+        <v>6918866</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2614,7 +2596,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2624,7 +2606,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2639,22 +2621,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120063670</v>
+        <v>120064680</v>
       </c>
       <c r="B19" t="n">
-        <v>78263</v>
+        <v>95455</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2667,21 +2649,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>53</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2691,10 +2673,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>503181</v>
+        <v>503081</v>
       </c>
       <c r="R19" t="n">
-        <v>6918937</v>
+        <v>6919157</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2726,7 +2708,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2736,7 +2718,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2763,10 +2745,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120064431</v>
+        <v>120064743</v>
       </c>
       <c r="B20" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2775,38 +2757,47 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>503138</v>
+        <v>503071</v>
       </c>
       <c r="R20" t="n">
-        <v>6919076</v>
+        <v>6919178</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2875,10 +2866,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120064680</v>
+        <v>120063775</v>
       </c>
       <c r="B21" t="n">
-        <v>95455</v>
+        <v>91840</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2887,41 +2878,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>503081</v>
+        <v>503180</v>
       </c>
       <c r="R21" t="n">
-        <v>6919157</v>
+        <v>6918964</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2950,7 +2941,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2960,7 +2951,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2975,22 +2966,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120062915</v>
+        <v>120064431</v>
       </c>
       <c r="B22" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3003,34 +2994,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503303</v>
+        <v>503138</v>
       </c>
       <c r="R22" t="n">
-        <v>6918868</v>
+        <v>6919076</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3099,10 +3090,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120063666</v>
+        <v>120064281</v>
       </c>
       <c r="B23" t="n">
-        <v>79115</v>
+        <v>97907</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3111,41 +3102,50 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>503181</v>
+        <v>503147</v>
       </c>
       <c r="R23" t="n">
-        <v>6918937</v>
+        <v>6919079</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3199,12 +3199,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 39496-2024 artfynd.xlsx
+++ b/artfynd/A 39496-2024 artfynd.xlsx
@@ -2521,10 +2521,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120062610</v>
+        <v>120064680</v>
       </c>
       <c r="B18" t="n">
-        <v>78263</v>
+        <v>95455</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2537,21 +2537,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>53</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2561,10 +2561,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>503313</v>
+        <v>503081</v>
       </c>
       <c r="R18" t="n">
-        <v>6918866</v>
+        <v>6919157</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2633,10 +2633,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120064680</v>
+        <v>120062610</v>
       </c>
       <c r="B19" t="n">
-        <v>95455</v>
+        <v>78263</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2649,21 +2649,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>53</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>503081</v>
+        <v>503313</v>
       </c>
       <c r="R19" t="n">
-        <v>6919157</v>
+        <v>6918866</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 39496-2024 artfynd.xlsx
+++ b/artfynd/A 39496-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120062695</v>
+        <v>120063873</v>
       </c>
       <c r="B2" t="n">
         <v>97907</v>
@@ -710,7 +710,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>503271</v>
+        <v>503181</v>
       </c>
       <c r="R2" t="n">
-        <v>6918864</v>
+        <v>6918946</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,19 +784,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120064120</v>
+        <v>120064032</v>
       </c>
       <c r="B3" t="n">
         <v>97907</v>
@@ -824,29 +829,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503169</v>
+        <v>503163</v>
       </c>
       <c r="R3" t="n">
-        <v>6919008</v>
+        <v>6919011</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -885,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,22 +896,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120063873</v>
+        <v>120064431</v>
       </c>
       <c r="B4" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,50 +920,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503181</v>
+        <v>503138</v>
       </c>
       <c r="R4" t="n">
-        <v>6918946</v>
+        <v>6919076</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -996,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1006,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,22 +1008,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120063670</v>
+        <v>120064366</v>
       </c>
       <c r="B5" t="n">
-        <v>78263</v>
+        <v>79607</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1049,21 +1036,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1073,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503181</v>
+        <v>503147</v>
       </c>
       <c r="R5" t="n">
-        <v>6918937</v>
+        <v>6919083</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1108,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1118,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1145,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120064457</v>
+        <v>120063666</v>
       </c>
       <c r="B6" t="n">
-        <v>97907</v>
+        <v>79115</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1157,41 +1144,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503135</v>
+        <v>503181</v>
       </c>
       <c r="R6" t="n">
-        <v>6919127</v>
+        <v>6918937</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1220,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1230,7 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,19 +1232,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120064397</v>
+        <v>120063854</v>
       </c>
       <c r="B7" t="n">
         <v>97907</v>
@@ -1292,7 +1279,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1302,17 +1289,17 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>503150</v>
+        <v>503171</v>
       </c>
       <c r="R7" t="n">
-        <v>6919090</v>
+        <v>6918993</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1341,7 +1328,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1351,7 +1338,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1366,19 +1353,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120063854</v>
+        <v>120064743</v>
       </c>
       <c r="B8" t="n">
         <v>97907</v>
@@ -1427,10 +1414,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>503171</v>
+        <v>503071</v>
       </c>
       <c r="R8" t="n">
-        <v>6918993</v>
+        <v>6919178</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1499,10 +1486,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120063353</v>
+        <v>120063290</v>
       </c>
       <c r="B9" t="n">
-        <v>78263</v>
+        <v>90527</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1511,38 +1498,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>503182</v>
+        <v>503218</v>
       </c>
       <c r="R9" t="n">
-        <v>6918921</v>
+        <v>6918907</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1611,10 +1598,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120064738</v>
+        <v>120063670</v>
       </c>
       <c r="B10" t="n">
-        <v>79643</v>
+        <v>78263</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1623,25 +1610,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6464</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1651,10 +1638,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>503079</v>
+        <v>503181</v>
       </c>
       <c r="R10" t="n">
-        <v>6919159</v>
+        <v>6918937</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1686,7 +1673,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1696,7 +1683,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1723,10 +1710,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120063666</v>
+        <v>120063775</v>
       </c>
       <c r="B11" t="n">
-        <v>79115</v>
+        <v>91840</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1735,41 +1722,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>503181</v>
+        <v>503180</v>
       </c>
       <c r="R11" t="n">
-        <v>6918937</v>
+        <v>6918964</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1798,7 +1785,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1808,7 +1795,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1823,22 +1810,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120063751</v>
+        <v>120064680</v>
       </c>
       <c r="B12" t="n">
-        <v>97907</v>
+        <v>95455</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1847,50 +1834,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>503174</v>
+        <v>503081</v>
       </c>
       <c r="R12" t="n">
-        <v>6918958</v>
+        <v>6919157</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1919,7 +1897,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1929,7 +1907,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1944,22 +1922,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120062713</v>
+        <v>120064397</v>
       </c>
       <c r="B13" t="n">
-        <v>57326</v>
+        <v>97907</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1968,31 +1946,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2001,13 +1983,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>503279</v>
+        <v>503150</v>
       </c>
       <c r="R13" t="n">
-        <v>6918859</v>
+        <v>6919090</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2036,7 +2018,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2046,7 +2028,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2061,22 +2043,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120063290</v>
+        <v>120064738</v>
       </c>
       <c r="B14" t="n">
-        <v>90527</v>
+        <v>79643</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2089,21 +2071,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>6464</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2113,13 +2095,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>503218</v>
+        <v>503079</v>
       </c>
       <c r="R14" t="n">
-        <v>6918907</v>
+        <v>6919159</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2148,7 +2130,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2158,7 +2140,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2173,22 +2155,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120064366</v>
+        <v>120063353</v>
       </c>
       <c r="B15" t="n">
-        <v>79607</v>
+        <v>78263</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2201,37 +2183,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>503147</v>
+        <v>503182</v>
       </c>
       <c r="R15" t="n">
-        <v>6919083</v>
+        <v>6918921</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2260,7 +2242,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2270,7 +2252,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2285,19 +2267,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120064032</v>
+        <v>120064120</v>
       </c>
       <c r="B16" t="n">
         <v>97907</v>
@@ -2330,20 +2312,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>503163</v>
+        <v>503169</v>
       </c>
       <c r="R16" t="n">
-        <v>6919011</v>
+        <v>6919008</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2372,7 +2363,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2382,7 +2373,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2397,22 +2388,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120062915</v>
+        <v>120064457</v>
       </c>
       <c r="B17" t="n">
-        <v>91852</v>
+        <v>97907</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2421,38 +2412,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>503303</v>
+        <v>503135</v>
       </c>
       <c r="R17" t="n">
-        <v>6918868</v>
+        <v>6919127</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2521,10 +2512,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120064680</v>
+        <v>120062610</v>
       </c>
       <c r="B18" t="n">
-        <v>95455</v>
+        <v>78263</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2537,21 +2528,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2561,10 +2552,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>503081</v>
+        <v>503313</v>
       </c>
       <c r="R18" t="n">
-        <v>6919157</v>
+        <v>6918866</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2596,7 +2587,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2606,7 +2597,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2633,10 +2624,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120062610</v>
+        <v>120062915</v>
       </c>
       <c r="B19" t="n">
-        <v>78263</v>
+        <v>91852</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2645,25 +2636,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>4366</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2673,13 +2664,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>503313</v>
+        <v>503303</v>
       </c>
       <c r="R19" t="n">
-        <v>6918866</v>
+        <v>6918868</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2708,7 +2699,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2718,7 +2709,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2733,19 +2724,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120064743</v>
+        <v>120062695</v>
       </c>
       <c r="B20" t="n">
         <v>97907</v>
@@ -2783,21 +2774,16 @@
           <t>10</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>503071</v>
+        <v>503271</v>
       </c>
       <c r="R20" t="n">
-        <v>6919178</v>
+        <v>6918864</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2866,10 +2852,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120063775</v>
+        <v>120064281</v>
       </c>
       <c r="B21" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2878,38 +2864,47 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>503180</v>
+        <v>503147</v>
       </c>
       <c r="R21" t="n">
-        <v>6918964</v>
+        <v>6919079</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2978,10 +2973,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120064431</v>
+        <v>120063751</v>
       </c>
       <c r="B22" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2990,38 +2985,47 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503138</v>
+        <v>503174</v>
       </c>
       <c r="R22" t="n">
-        <v>6919076</v>
+        <v>6918958</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3090,10 +3094,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120064281</v>
+        <v>120062713</v>
       </c>
       <c r="B23" t="n">
-        <v>97907</v>
+        <v>57326</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3102,47 +3106,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>503147</v>
+        <v>503279</v>
       </c>
       <c r="R23" t="n">
-        <v>6919079</v>
+        <v>6918859</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 39496-2024 artfynd.xlsx
+++ b/artfynd/A 39496-2024 artfynd.xlsx
@@ -1365,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120064743</v>
+        <v>120063290</v>
       </c>
       <c r="B8" t="n">
-        <v>97907</v>
+        <v>90527</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,47 +1377,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>503071</v>
+        <v>503218</v>
       </c>
       <c r="R8" t="n">
-        <v>6919178</v>
+        <v>6918907</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1486,10 +1477,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120063290</v>
+        <v>120064743</v>
       </c>
       <c r="B9" t="n">
-        <v>90527</v>
+        <v>97907</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1498,38 +1489,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>503218</v>
+        <v>503071</v>
       </c>
       <c r="R9" t="n">
-        <v>6918907</v>
+        <v>6919178</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 39496-2024 artfynd.xlsx
+++ b/artfynd/A 39496-2024 artfynd.xlsx
@@ -1365,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120063290</v>
+        <v>120064743</v>
       </c>
       <c r="B8" t="n">
-        <v>90527</v>
+        <v>97907</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,38 +1377,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>503218</v>
+        <v>503071</v>
       </c>
       <c r="R8" t="n">
-        <v>6918907</v>
+        <v>6919178</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1477,10 +1486,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120064743</v>
+        <v>120063290</v>
       </c>
       <c r="B9" t="n">
-        <v>97907</v>
+        <v>90527</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1489,47 +1498,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>503071</v>
+        <v>503218</v>
       </c>
       <c r="R9" t="n">
-        <v>6919178</v>
+        <v>6918907</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 39496-2024 artfynd.xlsx
+++ b/artfynd/A 39496-2024 artfynd.xlsx
@@ -2512,10 +2512,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120062610</v>
+        <v>120062915</v>
       </c>
       <c r="B18" t="n">
-        <v>78263</v>
+        <v>91852</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2524,25 +2524,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>4366</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2552,13 +2552,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>503313</v>
+        <v>503303</v>
       </c>
       <c r="R18" t="n">
-        <v>6918866</v>
+        <v>6918868</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2612,22 +2612,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120062915</v>
+        <v>120062610</v>
       </c>
       <c r="B19" t="n">
-        <v>91852</v>
+        <v>78263</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2636,25 +2636,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4366</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2664,13 +2664,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>503303</v>
+        <v>503313</v>
       </c>
       <c r="R19" t="n">
-        <v>6918868</v>
+        <v>6918866</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2724,12 +2724,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 39496-2024 artfynd.xlsx
+++ b/artfynd/A 39496-2024 artfynd.xlsx
@@ -2512,10 +2512,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120062915</v>
+        <v>120062610</v>
       </c>
       <c r="B18" t="n">
-        <v>91852</v>
+        <v>78263</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2524,25 +2524,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4366</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2552,13 +2552,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>503303</v>
+        <v>503313</v>
       </c>
       <c r="R18" t="n">
-        <v>6918868</v>
+        <v>6918866</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2612,22 +2612,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120062610</v>
+        <v>120062915</v>
       </c>
       <c r="B19" t="n">
-        <v>78263</v>
+        <v>91852</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2636,25 +2636,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>4366</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2664,13 +2664,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>503313</v>
+        <v>503303</v>
       </c>
       <c r="R19" t="n">
-        <v>6918866</v>
+        <v>6918868</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2724,12 +2724,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 39496-2024 artfynd.xlsx
+++ b/artfynd/A 39496-2024 artfynd.xlsx
@@ -1365,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120064743</v>
+        <v>120063290</v>
       </c>
       <c r="B8" t="n">
-        <v>97907</v>
+        <v>90527</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,47 +1377,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>503071</v>
+        <v>503218</v>
       </c>
       <c r="R8" t="n">
-        <v>6919178</v>
+        <v>6918907</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1486,10 +1477,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120063290</v>
+        <v>120064743</v>
       </c>
       <c r="B9" t="n">
-        <v>90527</v>
+        <v>97907</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1498,38 +1489,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>503218</v>
+        <v>503071</v>
       </c>
       <c r="R9" t="n">
-        <v>6918907</v>
+        <v>6919178</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -2512,10 +2512,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120062610</v>
+        <v>120062915</v>
       </c>
       <c r="B18" t="n">
-        <v>78263</v>
+        <v>91852</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2524,25 +2524,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>4366</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2552,13 +2552,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>503313</v>
+        <v>503303</v>
       </c>
       <c r="R18" t="n">
-        <v>6918866</v>
+        <v>6918868</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2612,22 +2612,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120062915</v>
+        <v>120062610</v>
       </c>
       <c r="B19" t="n">
-        <v>91852</v>
+        <v>78263</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2636,25 +2636,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4366</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2664,13 +2664,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>503303</v>
+        <v>503313</v>
       </c>
       <c r="R19" t="n">
-        <v>6918868</v>
+        <v>6918866</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2724,12 +2724,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 39496-2024 artfynd.xlsx
+++ b/artfynd/A 39496-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120063873</v>
+        <v>120064032</v>
       </c>
       <c r="B2" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -708,29 +708,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>503181</v>
+        <v>503163</v>
       </c>
       <c r="R2" t="n">
-        <v>6918946</v>
+        <v>6919011</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120064032</v>
+        <v>120064281</v>
       </c>
       <c r="B3" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -829,17 +820,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503163</v>
+        <v>503147</v>
       </c>
       <c r="R3" t="n">
-        <v>6919011</v>
+        <v>6919079</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -908,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120064431</v>
+        <v>120064366</v>
       </c>
       <c r="B4" t="n">
-        <v>91840</v>
+        <v>79623</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,41 +920,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503138</v>
+        <v>503147</v>
       </c>
       <c r="R4" t="n">
-        <v>6919076</v>
+        <v>6919083</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,22 +1008,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120064366</v>
+        <v>120064397</v>
       </c>
       <c r="B5" t="n">
-        <v>79607</v>
+        <v>97930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,38 +1032,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503147</v>
+        <v>503150</v>
       </c>
       <c r="R5" t="n">
-        <v>6919083</v>
+        <v>6919090</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1095,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1114,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,10 +1141,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120063666</v>
+        <v>120064457</v>
       </c>
       <c r="B6" t="n">
-        <v>79115</v>
+        <v>97930</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,41 +1153,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503181</v>
+        <v>503135</v>
       </c>
       <c r="R6" t="n">
-        <v>6918937</v>
+        <v>6919127</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1207,7 +1216,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1226,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,22 +1241,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120063854</v>
+        <v>120063353</v>
       </c>
       <c r="B7" t="n">
-        <v>97907</v>
+        <v>78279</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,47 +1265,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>503171</v>
+        <v>503182</v>
       </c>
       <c r="R7" t="n">
-        <v>6918993</v>
+        <v>6918921</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1365,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120063290</v>
+        <v>120064431</v>
       </c>
       <c r="B8" t="n">
-        <v>90527</v>
+        <v>91858</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1381,34 +1381,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>503218</v>
+        <v>503138</v>
       </c>
       <c r="R8" t="n">
-        <v>6918907</v>
+        <v>6919076</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1477,10 +1477,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120064743</v>
+        <v>120062610</v>
       </c>
       <c r="B9" t="n">
-        <v>97907</v>
+        <v>78279</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1489,50 +1489,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>503071</v>
+        <v>503313</v>
       </c>
       <c r="R9" t="n">
-        <v>6919178</v>
+        <v>6918866</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1561,7 +1552,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1571,7 +1562,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,22 +1577,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120063670</v>
+        <v>120063873</v>
       </c>
       <c r="B10" t="n">
-        <v>78263</v>
+        <v>97930</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1610,28 +1601,37 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Källmyran, Källmyran, Mpd</t>
@@ -1641,7 +1641,7 @@
         <v>503181</v>
       </c>
       <c r="R10" t="n">
-        <v>6918937</v>
+        <v>6918946</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1710,10 +1710,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120063775</v>
+        <v>120063666</v>
       </c>
       <c r="B11" t="n">
-        <v>91840</v>
+        <v>79131</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1722,41 +1722,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>503180</v>
+        <v>503181</v>
       </c>
       <c r="R11" t="n">
-        <v>6918964</v>
+        <v>6918937</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1810,22 +1810,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120064680</v>
+        <v>120064743</v>
       </c>
       <c r="B12" t="n">
-        <v>95455</v>
+        <v>97930</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1834,41 +1834,50 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>503081</v>
+        <v>503071</v>
       </c>
       <c r="R12" t="n">
-        <v>6919157</v>
+        <v>6919178</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1897,7 +1906,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1907,7 +1916,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1922,22 +1931,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120064397</v>
+        <v>120063854</v>
       </c>
       <c r="B13" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1969,7 +1978,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1979,17 +1988,17 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>503150</v>
+        <v>503171</v>
       </c>
       <c r="R13" t="n">
-        <v>6919090</v>
+        <v>6918993</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2018,7 +2027,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2028,7 +2037,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2043,22 +2052,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120064738</v>
+        <v>120063290</v>
       </c>
       <c r="B14" t="n">
-        <v>79643</v>
+        <v>90545</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2071,21 +2080,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6464</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2095,13 +2104,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>503079</v>
+        <v>503218</v>
       </c>
       <c r="R14" t="n">
-        <v>6919159</v>
+        <v>6918907</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2130,7 +2139,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2140,7 +2149,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2155,22 +2164,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120063353</v>
+        <v>120063775</v>
       </c>
       <c r="B15" t="n">
-        <v>78263</v>
+        <v>91858</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2179,25 +2188,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2207,10 +2216,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>503182</v>
+        <v>503180</v>
       </c>
       <c r="R15" t="n">
-        <v>6918921</v>
+        <v>6918964</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2279,10 +2288,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120064120</v>
+        <v>120063751</v>
       </c>
       <c r="B16" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2314,7 +2323,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2324,17 +2333,17 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>503169</v>
+        <v>503174</v>
       </c>
       <c r="R16" t="n">
-        <v>6919008</v>
+        <v>6918958</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2363,7 +2372,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2373,7 +2382,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2388,22 +2397,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120064457</v>
+        <v>120064738</v>
       </c>
       <c r="B17" t="n">
-        <v>97907</v>
+        <v>79659</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2412,41 +2421,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>503135</v>
+        <v>503079</v>
       </c>
       <c r="R17" t="n">
-        <v>6919127</v>
+        <v>6919159</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2475,7 +2484,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2485,7 +2494,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2500,22 +2509,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120062915</v>
+        <v>120064120</v>
       </c>
       <c r="B18" t="n">
-        <v>91852</v>
+        <v>97930</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2524,41 +2533,50 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>503303</v>
+        <v>503169</v>
       </c>
       <c r="R18" t="n">
-        <v>6918868</v>
+        <v>6919008</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2587,7 +2605,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2597,7 +2615,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2612,22 +2630,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120062610</v>
+        <v>120062695</v>
       </c>
       <c r="B19" t="n">
-        <v>78263</v>
+        <v>97930</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2636,41 +2654,45 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>503313</v>
+        <v>503271</v>
       </c>
       <c r="R19" t="n">
-        <v>6918866</v>
+        <v>6918864</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2699,7 +2721,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2709,7 +2731,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2724,22 +2746,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120062695</v>
+        <v>120064680</v>
       </c>
       <c r="B20" t="n">
-        <v>97907</v>
+        <v>95478</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2748,45 +2770,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>503271</v>
+        <v>503081</v>
       </c>
       <c r="R20" t="n">
-        <v>6918864</v>
+        <v>6919157</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2815,7 +2833,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2825,7 +2843,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2840,22 +2858,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120064281</v>
+        <v>120062713</v>
       </c>
       <c r="B21" t="n">
-        <v>97907</v>
+        <v>57336</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2864,47 +2882,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>503147</v>
+        <v>503279</v>
       </c>
       <c r="R21" t="n">
-        <v>6919079</v>
+        <v>6918859</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2973,10 +2987,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120063751</v>
+        <v>120063670</v>
       </c>
       <c r="B22" t="n">
-        <v>97907</v>
+        <v>78279</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2985,50 +2999,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503174</v>
+        <v>503181</v>
       </c>
       <c r="R22" t="n">
-        <v>6918958</v>
+        <v>6918937</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3057,7 +3062,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3067,7 +3072,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3082,22 +3087,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120062713</v>
+        <v>120062915</v>
       </c>
       <c r="B23" t="n">
-        <v>57326</v>
+        <v>91870</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3106,43 +3111,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>4366</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>503279</v>
+        <v>503303</v>
       </c>
       <c r="R23" t="n">
-        <v>6918859</v>
+        <v>6918868</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 39496-2024 artfynd.xlsx
+++ b/artfynd/A 39496-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120064032</v>
+        <v>120063290</v>
       </c>
       <c r="B2" t="n">
-        <v>97930</v>
+        <v>90545</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>503163</v>
+        <v>503218</v>
       </c>
       <c r="R2" t="n">
-        <v>6919011</v>
+        <v>6918907</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120064281</v>
+        <v>120064397</v>
       </c>
       <c r="B3" t="n">
         <v>97930</v>
@@ -822,7 +822,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503147</v>
+        <v>503150</v>
       </c>
       <c r="R3" t="n">
-        <v>6919079</v>
+        <v>6919090</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,22 +896,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120064366</v>
+        <v>120064738</v>
       </c>
       <c r="B4" t="n">
-        <v>79623</v>
+        <v>79659</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,25 +920,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503147</v>
+        <v>503079</v>
       </c>
       <c r="R4" t="n">
-        <v>6919083</v>
+        <v>6919159</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -983,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,7 +1020,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120064397</v>
+        <v>120064743</v>
       </c>
       <c r="B5" t="n">
         <v>97930</v>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1065,17 +1065,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503150</v>
+        <v>503071</v>
       </c>
       <c r="R5" t="n">
-        <v>6919090</v>
+        <v>6919178</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,22 +1129,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120064457</v>
+        <v>120063670</v>
       </c>
       <c r="B6" t="n">
-        <v>97930</v>
+        <v>78279</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1153,41 +1153,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503135</v>
+        <v>503181</v>
       </c>
       <c r="R6" t="n">
-        <v>6919127</v>
+        <v>6918937</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1241,22 +1241,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120063353</v>
+        <v>120064366</v>
       </c>
       <c r="B7" t="n">
-        <v>78279</v>
+        <v>79623</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1269,37 +1269,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>503182</v>
+        <v>503147</v>
       </c>
       <c r="R7" t="n">
-        <v>6918921</v>
+        <v>6919083</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1353,12 +1353,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1477,10 +1477,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120062610</v>
+        <v>120064680</v>
       </c>
       <c r="B9" t="n">
-        <v>78279</v>
+        <v>95478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1493,21 +1493,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>53</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1517,10 +1517,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>503313</v>
+        <v>503081</v>
       </c>
       <c r="R9" t="n">
-        <v>6918866</v>
+        <v>6919157</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1589,10 +1589,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120063873</v>
+        <v>120062713</v>
       </c>
       <c r="B10" t="n">
-        <v>97930</v>
+        <v>57336</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1601,35 +1601,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1638,13 +1634,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>503181</v>
+        <v>503279</v>
       </c>
       <c r="R10" t="n">
-        <v>6918946</v>
+        <v>6918859</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1673,7 +1669,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1683,7 +1679,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1698,22 +1694,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120063666</v>
+        <v>120064032</v>
       </c>
       <c r="B11" t="n">
-        <v>79131</v>
+        <v>97930</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1722,41 +1718,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>503181</v>
+        <v>503163</v>
       </c>
       <c r="R11" t="n">
-        <v>6918937</v>
+        <v>6919011</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1785,7 +1781,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1795,7 +1791,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1810,19 +1806,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120064743</v>
+        <v>120064457</v>
       </c>
       <c r="B12" t="n">
         <v>97930</v>
@@ -1855,26 +1851,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>503071</v>
+        <v>503135</v>
       </c>
       <c r="R12" t="n">
-        <v>6919178</v>
+        <v>6919127</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2064,10 +2051,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120063290</v>
+        <v>120062610</v>
       </c>
       <c r="B14" t="n">
-        <v>90545</v>
+        <v>78279</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2076,25 +2063,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2104,13 +2091,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>503218</v>
+        <v>503313</v>
       </c>
       <c r="R14" t="n">
-        <v>6918907</v>
+        <v>6918866</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2139,7 +2126,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2149,7 +2136,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2164,22 +2151,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120063775</v>
+        <v>120063666</v>
       </c>
       <c r="B15" t="n">
-        <v>91858</v>
+        <v>79131</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2188,41 +2175,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>503180</v>
+        <v>503181</v>
       </c>
       <c r="R15" t="n">
-        <v>6918964</v>
+        <v>6918937</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2251,7 +2238,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2261,7 +2248,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2276,22 +2263,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120063751</v>
+        <v>120063775</v>
       </c>
       <c r="B16" t="n">
-        <v>97930</v>
+        <v>91858</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2300,47 +2287,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>503174</v>
+        <v>503180</v>
       </c>
       <c r="R16" t="n">
-        <v>6918958</v>
+        <v>6918964</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2409,10 +2387,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120064738</v>
+        <v>120062915</v>
       </c>
       <c r="B17" t="n">
-        <v>79659</v>
+        <v>91870</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2425,21 +2403,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6464</v>
+        <v>4366</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2449,13 +2427,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>503079</v>
+        <v>503303</v>
       </c>
       <c r="R17" t="n">
-        <v>6919159</v>
+        <v>6918868</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2484,7 +2462,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2494,7 +2472,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2509,19 +2487,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120064120</v>
+        <v>120063751</v>
       </c>
       <c r="B18" t="n">
         <v>97930</v>
@@ -2556,7 +2534,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2566,17 +2544,17 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>503169</v>
+        <v>503174</v>
       </c>
       <c r="R18" t="n">
-        <v>6919008</v>
+        <v>6918958</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2605,7 +2583,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2615,7 +2593,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2630,12 +2608,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2758,10 +2736,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120064680</v>
+        <v>120064120</v>
       </c>
       <c r="B20" t="n">
-        <v>95478</v>
+        <v>97930</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2770,38 +2748,47 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>503081</v>
+        <v>503169</v>
       </c>
       <c r="R20" t="n">
-        <v>6919157</v>
+        <v>6919008</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2833,7 +2820,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2843,7 +2830,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2870,10 +2857,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120062713</v>
+        <v>120063873</v>
       </c>
       <c r="B21" t="n">
-        <v>57336</v>
+        <v>97930</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2882,31 +2869,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2915,13 +2906,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>503279</v>
+        <v>503181</v>
       </c>
       <c r="R21" t="n">
-        <v>6918859</v>
+        <v>6918946</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2950,7 +2941,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2960,7 +2951,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2975,22 +2966,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120063670</v>
+        <v>120064281</v>
       </c>
       <c r="B22" t="n">
-        <v>78279</v>
+        <v>97930</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2999,41 +2990,50 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503181</v>
+        <v>503147</v>
       </c>
       <c r="R22" t="n">
-        <v>6918937</v>
+        <v>6919079</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3087,22 +3087,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120062915</v>
+        <v>120063353</v>
       </c>
       <c r="B23" t="n">
-        <v>91870</v>
+        <v>78279</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3111,38 +3111,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4366</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>503303</v>
+        <v>503182</v>
       </c>
       <c r="R23" t="n">
-        <v>6918868</v>
+        <v>6918921</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 39496-2024 artfynd.xlsx
+++ b/artfynd/A 39496-2024 artfynd.xlsx
@@ -1141,10 +1141,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120063670</v>
+        <v>120064366</v>
       </c>
       <c r="B6" t="n">
-        <v>78279</v>
+        <v>79623</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1157,21 +1157,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503181</v>
+        <v>503147</v>
       </c>
       <c r="R6" t="n">
-        <v>6918937</v>
+        <v>6919083</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,10 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120064366</v>
+        <v>120063670</v>
       </c>
       <c r="B7" t="n">
-        <v>79623</v>
+        <v>78279</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1269,21 +1269,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1293,10 +1293,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>503147</v>
+        <v>503181</v>
       </c>
       <c r="R7" t="n">
-        <v>6919083</v>
+        <v>6918937</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -2387,10 +2387,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120062915</v>
+        <v>120063751</v>
       </c>
       <c r="B17" t="n">
-        <v>91870</v>
+        <v>97930</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2399,38 +2399,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>503303</v>
+        <v>503174</v>
       </c>
       <c r="R17" t="n">
-        <v>6918868</v>
+        <v>6918958</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2499,10 +2508,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120063751</v>
+        <v>120062915</v>
       </c>
       <c r="B18" t="n">
-        <v>97930</v>
+        <v>91870</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2511,47 +2520,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>503174</v>
+        <v>503303</v>
       </c>
       <c r="R18" t="n">
-        <v>6918958</v>
+        <v>6918868</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 39496-2024 artfynd.xlsx
+++ b/artfynd/A 39496-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120063290</v>
+        <v>120064281</v>
       </c>
       <c r="B2" t="n">
-        <v>90545</v>
+        <v>97930</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>503218</v>
+        <v>503147</v>
       </c>
       <c r="R2" t="n">
-        <v>6918907</v>
+        <v>6919079</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120064397</v>
+        <v>120063751</v>
       </c>
       <c r="B3" t="n">
         <v>97930</v>
@@ -822,7 +831,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -832,17 +841,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503150</v>
+        <v>503174</v>
       </c>
       <c r="R3" t="n">
-        <v>6919090</v>
+        <v>6918958</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,22 +905,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120064738</v>
+        <v>120062610</v>
       </c>
       <c r="B4" t="n">
-        <v>79659</v>
+        <v>78279</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,25 +929,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6464</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -948,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503079</v>
+        <v>503313</v>
       </c>
       <c r="R4" t="n">
-        <v>6919159</v>
+        <v>6918866</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -983,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +1002,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120064743</v>
+        <v>120063775</v>
       </c>
       <c r="B5" t="n">
-        <v>97930</v>
+        <v>91858</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,47 +1041,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503071</v>
+        <v>503180</v>
       </c>
       <c r="R5" t="n">
-        <v>6919178</v>
+        <v>6918964</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1141,10 +1141,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120064366</v>
+        <v>120064457</v>
       </c>
       <c r="B6" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1153,41 +1153,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503147</v>
+        <v>503135</v>
       </c>
       <c r="R6" t="n">
-        <v>6919083</v>
+        <v>6919127</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1241,22 +1241,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120063670</v>
+        <v>120063873</v>
       </c>
       <c r="B7" t="n">
-        <v>78279</v>
+        <v>97930</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,28 +1265,37 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Källmyran, Källmyran, Mpd</t>
@@ -1296,7 +1305,7 @@
         <v>503181</v>
       </c>
       <c r="R7" t="n">
-        <v>6918937</v>
+        <v>6918946</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1328,7 +1337,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1338,7 +1347,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,10 +1374,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120064431</v>
+        <v>120063666</v>
       </c>
       <c r="B8" t="n">
-        <v>91858</v>
+        <v>79131</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,41 +1386,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>503138</v>
+        <v>503181</v>
       </c>
       <c r="R8" t="n">
-        <v>6919076</v>
+        <v>6918937</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1440,7 +1449,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1450,7 +1459,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1465,22 +1474,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120064680</v>
+        <v>120064743</v>
       </c>
       <c r="B9" t="n">
-        <v>95478</v>
+        <v>97930</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1489,41 +1498,50 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>503081</v>
+        <v>503071</v>
       </c>
       <c r="R9" t="n">
-        <v>6919157</v>
+        <v>6919178</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1552,7 +1570,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1562,7 +1580,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1577,22 +1595,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120062713</v>
+        <v>120064032</v>
       </c>
       <c r="B10" t="n">
-        <v>57336</v>
+        <v>97930</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1601,43 +1619,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>503279</v>
+        <v>503163</v>
       </c>
       <c r="R10" t="n">
-        <v>6918859</v>
+        <v>6919011</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1706,10 +1719,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120064032</v>
+        <v>120064738</v>
       </c>
       <c r="B11" t="n">
-        <v>97930</v>
+        <v>79659</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1718,41 +1731,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>503163</v>
+        <v>503079</v>
       </c>
       <c r="R11" t="n">
-        <v>6919011</v>
+        <v>6919159</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1781,7 +1794,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1791,7 +1804,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1806,22 +1819,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120064457</v>
+        <v>120062915</v>
       </c>
       <c r="B12" t="n">
-        <v>97930</v>
+        <v>91870</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1830,38 +1843,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>503135</v>
+        <v>503303</v>
       </c>
       <c r="R12" t="n">
-        <v>6919127</v>
+        <v>6918868</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1930,7 +1943,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120063854</v>
+        <v>120064397</v>
       </c>
       <c r="B13" t="n">
         <v>97930</v>
@@ -1965,7 +1978,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1975,17 +1988,17 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>503171</v>
+        <v>503150</v>
       </c>
       <c r="R13" t="n">
-        <v>6918993</v>
+        <v>6919090</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2014,7 +2027,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2024,7 +2037,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2039,22 +2052,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120062610</v>
+        <v>120063854</v>
       </c>
       <c r="B14" t="n">
-        <v>78279</v>
+        <v>97930</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2063,41 +2076,50 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>503313</v>
+        <v>503171</v>
       </c>
       <c r="R14" t="n">
-        <v>6918866</v>
+        <v>6918993</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2126,7 +2148,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2136,7 +2158,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2151,22 +2173,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120063666</v>
+        <v>120064680</v>
       </c>
       <c r="B15" t="n">
-        <v>79131</v>
+        <v>95478</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2179,21 +2201,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229821</v>
+        <v>53</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2203,10 +2225,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>503181</v>
+        <v>503081</v>
       </c>
       <c r="R15" t="n">
-        <v>6918937</v>
+        <v>6919157</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2238,7 +2260,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2248,7 +2270,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2275,10 +2297,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120063775</v>
+        <v>120063290</v>
       </c>
       <c r="B16" t="n">
-        <v>91858</v>
+        <v>90545</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2291,34 +2313,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>503180</v>
+        <v>503218</v>
       </c>
       <c r="R16" t="n">
-        <v>6918964</v>
+        <v>6918907</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2387,10 +2409,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120063751</v>
+        <v>120063670</v>
       </c>
       <c r="B17" t="n">
-        <v>97930</v>
+        <v>78279</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2399,50 +2421,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>503174</v>
+        <v>503181</v>
       </c>
       <c r="R17" t="n">
-        <v>6918958</v>
+        <v>6918937</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2471,7 +2484,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2481,7 +2494,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2496,22 +2509,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120062915</v>
+        <v>120064431</v>
       </c>
       <c r="B18" t="n">
-        <v>91870</v>
+        <v>91858</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2524,34 +2537,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>503303</v>
+        <v>503138</v>
       </c>
       <c r="R18" t="n">
-        <v>6918868</v>
+        <v>6919076</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2620,10 +2633,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120062695</v>
+        <v>120064366</v>
       </c>
       <c r="B19" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2632,45 +2645,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>503271</v>
+        <v>503147</v>
       </c>
       <c r="R19" t="n">
-        <v>6918864</v>
+        <v>6919083</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2699,7 +2708,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2709,7 +2718,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2724,22 +2733,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120064120</v>
+        <v>120062713</v>
       </c>
       <c r="B20" t="n">
-        <v>97930</v>
+        <v>57336</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2748,35 +2757,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2785,13 +2790,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>503169</v>
+        <v>503279</v>
       </c>
       <c r="R20" t="n">
-        <v>6919008</v>
+        <v>6918859</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2820,7 +2825,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2830,7 +2835,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2845,19 +2850,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120063873</v>
+        <v>120062695</v>
       </c>
       <c r="B21" t="n">
         <v>97930</v>
@@ -2892,12 +2897,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2906,13 +2906,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>503181</v>
+        <v>503271</v>
       </c>
       <c r="R21" t="n">
-        <v>6918946</v>
+        <v>6918864</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2966,22 +2966,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120064281</v>
+        <v>120063353</v>
       </c>
       <c r="B22" t="n">
-        <v>97930</v>
+        <v>78279</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2990,47 +2990,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503147</v>
+        <v>503182</v>
       </c>
       <c r="R22" t="n">
-        <v>6919079</v>
+        <v>6918921</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3099,10 +3090,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120063353</v>
+        <v>120064120</v>
       </c>
       <c r="B23" t="n">
-        <v>78279</v>
+        <v>97930</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3111,41 +3102,50 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>503182</v>
+        <v>503169</v>
       </c>
       <c r="R23" t="n">
-        <v>6918921</v>
+        <v>6919008</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3199,12 +3199,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 39496-2024 artfynd.xlsx
+++ b/artfynd/A 39496-2024 artfynd.xlsx
@@ -1486,7 +1486,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120064743</v>
+        <v>120064032</v>
       </c>
       <c r="B9" t="n">
         <v>97930</v>
@@ -1519,26 +1519,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>503071</v>
+        <v>503163</v>
       </c>
       <c r="R9" t="n">
-        <v>6919178</v>
+        <v>6919011</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1607,7 +1598,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120064032</v>
+        <v>120064743</v>
       </c>
       <c r="B10" t="n">
         <v>97930</v>
@@ -1640,17 +1631,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>503163</v>
+        <v>503071</v>
       </c>
       <c r="R10" t="n">
-        <v>6919011</v>
+        <v>6919178</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 39496-2024 artfynd.xlsx
+++ b/artfynd/A 39496-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120064281</v>
+        <v>120064431</v>
       </c>
       <c r="B2" t="n">
-        <v>97930</v>
+        <v>91858</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>503147</v>
+        <v>503138</v>
       </c>
       <c r="R2" t="n">
-        <v>6919079</v>
+        <v>6919076</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -796,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120063751</v>
+        <v>120064457</v>
       </c>
       <c r="B3" t="n">
         <v>97930</v>
@@ -829,26 +820,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503174</v>
+        <v>503135</v>
       </c>
       <c r="R3" t="n">
-        <v>6918958</v>
+        <v>6919127</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -917,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120062610</v>
+        <v>120063873</v>
       </c>
       <c r="B4" t="n">
-        <v>78279</v>
+        <v>97930</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,38 +911,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503313</v>
+        <v>503181</v>
       </c>
       <c r="R4" t="n">
-        <v>6918866</v>
+        <v>6918946</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -992,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120063775</v>
+        <v>120064397</v>
       </c>
       <c r="B5" t="n">
-        <v>91858</v>
+        <v>97930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,41 +1032,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503180</v>
+        <v>503150</v>
       </c>
       <c r="R5" t="n">
-        <v>6918964</v>
+        <v>6919090</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,22 +1129,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120064457</v>
+        <v>120063666</v>
       </c>
       <c r="B6" t="n">
-        <v>97930</v>
+        <v>79131</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1153,41 +1153,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503135</v>
+        <v>503181</v>
       </c>
       <c r="R6" t="n">
-        <v>6919127</v>
+        <v>6918937</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1241,22 +1241,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120063873</v>
+        <v>120063670</v>
       </c>
       <c r="B7" t="n">
-        <v>97930</v>
+        <v>78279</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,37 +1265,28 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Källmyran, Källmyran, Mpd</t>
@@ -1305,7 +1296,7 @@
         <v>503181</v>
       </c>
       <c r="R7" t="n">
-        <v>6918946</v>
+        <v>6918937</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1337,7 +1328,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1347,7 +1338,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1374,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120063666</v>
+        <v>120064738</v>
       </c>
       <c r="B8" t="n">
-        <v>79131</v>
+        <v>79659</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1386,25 +1377,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>6464</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1414,10 +1405,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>503181</v>
+        <v>503079</v>
       </c>
       <c r="R8" t="n">
-        <v>6918937</v>
+        <v>6919159</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1449,7 +1440,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1459,7 +1450,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1486,7 +1477,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120064032</v>
+        <v>120064743</v>
       </c>
       <c r="B9" t="n">
         <v>97930</v>
@@ -1519,17 +1510,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>503163</v>
+        <v>503071</v>
       </c>
       <c r="R9" t="n">
-        <v>6919011</v>
+        <v>6919178</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120064743</v>
+        <v>120063775</v>
       </c>
       <c r="B10" t="n">
-        <v>97930</v>
+        <v>91858</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1610,47 +1610,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>503071</v>
+        <v>503180</v>
       </c>
       <c r="R10" t="n">
-        <v>6919178</v>
+        <v>6918964</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1719,10 +1710,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120064738</v>
+        <v>120062915</v>
       </c>
       <c r="B11" t="n">
-        <v>79659</v>
+        <v>91870</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1735,21 +1726,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6464</v>
+        <v>4366</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1759,13 +1750,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>503079</v>
+        <v>503303</v>
       </c>
       <c r="R11" t="n">
-        <v>6919159</v>
+        <v>6918868</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1794,7 +1785,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1804,7 +1795,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1819,22 +1810,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120062915</v>
+        <v>120064680</v>
       </c>
       <c r="B12" t="n">
-        <v>91870</v>
+        <v>95478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1843,25 +1834,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4366</v>
+        <v>53</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1871,13 +1862,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>503303</v>
+        <v>503081</v>
       </c>
       <c r="R12" t="n">
-        <v>6918868</v>
+        <v>6919157</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1906,7 +1897,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1916,7 +1907,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1931,22 +1922,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120064397</v>
+        <v>120062713</v>
       </c>
       <c r="B13" t="n">
-        <v>97930</v>
+        <v>57336</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1955,35 +1946,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1992,13 +1979,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>503150</v>
+        <v>503279</v>
       </c>
       <c r="R13" t="n">
-        <v>6919090</v>
+        <v>6918859</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2027,7 +2014,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2037,7 +2024,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2052,12 +2039,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2185,10 +2172,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120064680</v>
+        <v>120064366</v>
       </c>
       <c r="B15" t="n">
-        <v>95478</v>
+        <v>79623</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2201,21 +2188,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2225,10 +2212,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>503081</v>
+        <v>503147</v>
       </c>
       <c r="R15" t="n">
-        <v>6919157</v>
+        <v>6919083</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2260,7 +2247,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2270,7 +2257,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2297,10 +2284,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120063290</v>
+        <v>120064120</v>
       </c>
       <c r="B16" t="n">
-        <v>90545</v>
+        <v>97930</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2309,41 +2296,50 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>503218</v>
+        <v>503169</v>
       </c>
       <c r="R16" t="n">
-        <v>6918907</v>
+        <v>6919008</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2372,7 +2368,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2382,7 +2378,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2397,22 +2393,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120063670</v>
+        <v>120062695</v>
       </c>
       <c r="B17" t="n">
-        <v>78279</v>
+        <v>97930</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2421,41 +2417,45 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>503181</v>
+        <v>503271</v>
       </c>
       <c r="R17" t="n">
-        <v>6918937</v>
+        <v>6918864</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2509,22 +2509,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120064431</v>
+        <v>120063290</v>
       </c>
       <c r="B18" t="n">
-        <v>91858</v>
+        <v>90545</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2537,34 +2537,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>503138</v>
+        <v>503218</v>
       </c>
       <c r="R18" t="n">
-        <v>6919076</v>
+        <v>6918907</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2633,10 +2633,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120064366</v>
+        <v>120063751</v>
       </c>
       <c r="B19" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2645,41 +2645,50 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>503147</v>
+        <v>503174</v>
       </c>
       <c r="R19" t="n">
-        <v>6919083</v>
+        <v>6918958</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2708,7 +2717,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2718,7 +2727,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2733,22 +2742,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120062713</v>
+        <v>120063353</v>
       </c>
       <c r="B20" t="n">
-        <v>57336</v>
+        <v>78279</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2761,39 +2770,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>503279</v>
+        <v>503182</v>
       </c>
       <c r="R20" t="n">
-        <v>6918859</v>
+        <v>6918921</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2862,10 +2866,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120062695</v>
+        <v>120062610</v>
       </c>
       <c r="B21" t="n">
-        <v>97930</v>
+        <v>78279</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2874,45 +2878,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>503271</v>
+        <v>503313</v>
       </c>
       <c r="R21" t="n">
-        <v>6918864</v>
+        <v>6918866</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2966,22 +2966,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120063353</v>
+        <v>120064032</v>
       </c>
       <c r="B22" t="n">
-        <v>78279</v>
+        <v>97930</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2990,25 +2990,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3018,10 +3018,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503182</v>
+        <v>503163</v>
       </c>
       <c r="R22" t="n">
-        <v>6918921</v>
+        <v>6919011</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3090,7 +3090,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120064120</v>
+        <v>120064281</v>
       </c>
       <c r="B23" t="n">
         <v>97930</v>
@@ -3135,17 +3135,17 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>503169</v>
+        <v>503147</v>
       </c>
       <c r="R23" t="n">
-        <v>6919008</v>
+        <v>6919079</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3199,12 +3199,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 39496-2024 artfynd.xlsx
+++ b/artfynd/A 39496-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120064431</v>
+        <v>120063353</v>
       </c>
       <c r="B2" t="n">
-        <v>91858</v>
+        <v>78279</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>503138</v>
+        <v>503182</v>
       </c>
       <c r="R2" t="n">
-        <v>6919076</v>
+        <v>6918921</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120064457</v>
+        <v>120063290</v>
       </c>
       <c r="B3" t="n">
-        <v>97930</v>
+        <v>90545</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,38 +799,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503135</v>
+        <v>503218</v>
       </c>
       <c r="R3" t="n">
-        <v>6919127</v>
+        <v>6918907</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120063873</v>
+        <v>120064431</v>
       </c>
       <c r="B4" t="n">
-        <v>97930</v>
+        <v>91858</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,50 +911,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503181</v>
+        <v>503138</v>
       </c>
       <c r="R4" t="n">
-        <v>6918946</v>
+        <v>6919076</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,12 +999,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1141,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120063666</v>
+        <v>120063775</v>
       </c>
       <c r="B6" t="n">
-        <v>79131</v>
+        <v>91858</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1153,41 +1144,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503181</v>
+        <v>503180</v>
       </c>
       <c r="R6" t="n">
-        <v>6918937</v>
+        <v>6918964</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1216,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1226,7 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1241,22 +1232,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120063670</v>
+        <v>120064738</v>
       </c>
       <c r="B7" t="n">
-        <v>78279</v>
+        <v>79659</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,25 +1256,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6464</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1293,10 +1284,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>503181</v>
+        <v>503079</v>
       </c>
       <c r="R7" t="n">
-        <v>6918937</v>
+        <v>6919159</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1328,7 +1319,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1338,7 +1329,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,10 +1356,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120064738</v>
+        <v>120064032</v>
       </c>
       <c r="B8" t="n">
-        <v>79659</v>
+        <v>97930</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,41 +1368,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>503079</v>
+        <v>503163</v>
       </c>
       <c r="R8" t="n">
-        <v>6919159</v>
+        <v>6919011</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1440,7 +1431,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1450,7 +1441,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1465,22 +1456,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120064743</v>
+        <v>120062610</v>
       </c>
       <c r="B9" t="n">
-        <v>97930</v>
+        <v>78279</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1489,50 +1480,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>503071</v>
+        <v>503313</v>
       </c>
       <c r="R9" t="n">
-        <v>6919178</v>
+        <v>6918866</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1561,7 +1543,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1571,7 +1553,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,22 +1568,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120063775</v>
+        <v>120064120</v>
       </c>
       <c r="B10" t="n">
-        <v>91858</v>
+        <v>97930</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1610,41 +1592,50 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>503180</v>
+        <v>503169</v>
       </c>
       <c r="R10" t="n">
-        <v>6918964</v>
+        <v>6919008</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1673,7 +1664,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1683,7 +1674,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1698,22 +1689,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120062915</v>
+        <v>120064457</v>
       </c>
       <c r="B11" t="n">
-        <v>91870</v>
+        <v>97930</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1722,38 +1713,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>503303</v>
+        <v>503135</v>
       </c>
       <c r="R11" t="n">
-        <v>6918868</v>
+        <v>6919127</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1822,10 +1813,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120064680</v>
+        <v>120064743</v>
       </c>
       <c r="B12" t="n">
-        <v>95478</v>
+        <v>97930</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1834,41 +1825,50 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>503081</v>
+        <v>503071</v>
       </c>
       <c r="R12" t="n">
-        <v>6919157</v>
+        <v>6919178</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1922,22 +1922,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120062713</v>
+        <v>120064281</v>
       </c>
       <c r="B13" t="n">
-        <v>57336</v>
+        <v>97930</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1946,43 +1946,47 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>503279</v>
+        <v>503147</v>
       </c>
       <c r="R13" t="n">
-        <v>6918859</v>
+        <v>6919079</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2051,7 +2055,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120063854</v>
+        <v>120063751</v>
       </c>
       <c r="B14" t="n">
         <v>97930</v>
@@ -2086,7 +2090,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2100,10 +2104,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>503171</v>
+        <v>503174</v>
       </c>
       <c r="R14" t="n">
-        <v>6918993</v>
+        <v>6918958</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2172,10 +2176,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120064366</v>
+        <v>120063670</v>
       </c>
       <c r="B15" t="n">
-        <v>79623</v>
+        <v>78279</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2188,21 +2192,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2212,10 +2216,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>503147</v>
+        <v>503181</v>
       </c>
       <c r="R15" t="n">
-        <v>6919083</v>
+        <v>6918937</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2247,7 +2251,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2257,7 +2261,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2284,10 +2288,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120064120</v>
+        <v>120062915</v>
       </c>
       <c r="B16" t="n">
-        <v>97930</v>
+        <v>91870</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2296,50 +2300,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>503169</v>
+        <v>503303</v>
       </c>
       <c r="R16" t="n">
-        <v>6919008</v>
+        <v>6918868</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2368,7 +2363,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2378,7 +2373,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2393,12 +2388,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2521,10 +2516,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120063290</v>
+        <v>120064680</v>
       </c>
       <c r="B18" t="n">
-        <v>90545</v>
+        <v>95478</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2533,25 +2528,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2561,13 +2556,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>503218</v>
+        <v>503081</v>
       </c>
       <c r="R18" t="n">
-        <v>6918907</v>
+        <v>6919157</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2596,7 +2591,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2606,7 +2601,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2621,22 +2616,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120063751</v>
+        <v>120063666</v>
       </c>
       <c r="B19" t="n">
-        <v>97930</v>
+        <v>79131</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2645,50 +2640,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>503174</v>
+        <v>503181</v>
       </c>
       <c r="R19" t="n">
-        <v>6918958</v>
+        <v>6918937</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2717,7 +2703,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2727,7 +2713,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2742,22 +2728,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120063353</v>
+        <v>120062713</v>
       </c>
       <c r="B20" t="n">
-        <v>78279</v>
+        <v>57336</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2770,34 +2756,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>503182</v>
+        <v>503279</v>
       </c>
       <c r="R20" t="n">
-        <v>6918921</v>
+        <v>6918859</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2866,10 +2857,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120062610</v>
+        <v>120064366</v>
       </c>
       <c r="B21" t="n">
-        <v>78279</v>
+        <v>79623</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2882,21 +2873,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2906,10 +2897,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>503313</v>
+        <v>503147</v>
       </c>
       <c r="R21" t="n">
-        <v>6918866</v>
+        <v>6919083</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2941,7 +2932,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2951,7 +2942,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2978,7 +2969,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120064032</v>
+        <v>120063873</v>
       </c>
       <c r="B22" t="n">
         <v>97930</v>
@@ -3011,20 +3002,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503163</v>
+        <v>503181</v>
       </c>
       <c r="R22" t="n">
-        <v>6919011</v>
+        <v>6918946</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3078,19 +3078,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120064281</v>
+        <v>120063854</v>
       </c>
       <c r="B23" t="n">
         <v>97930</v>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3139,10 +3139,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>503147</v>
+        <v>503171</v>
       </c>
       <c r="R23" t="n">
-        <v>6919079</v>
+        <v>6918993</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 39496-2024 artfynd.xlsx
+++ b/artfynd/A 39496-2024 artfynd.xlsx
@@ -1580,7 +1580,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120064120</v>
+        <v>120064457</v>
       </c>
       <c r="B10" t="n">
         <v>97930</v>
@@ -1613,29 +1613,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>503169</v>
+        <v>503135</v>
       </c>
       <c r="R10" t="n">
-        <v>6919008</v>
+        <v>6919127</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1664,7 +1655,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1674,7 +1665,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1689,19 +1680,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120064457</v>
+        <v>120064120</v>
       </c>
       <c r="B11" t="n">
         <v>97930</v>
@@ -1734,20 +1725,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>503135</v>
+        <v>503169</v>
       </c>
       <c r="R11" t="n">
-        <v>6919127</v>
+        <v>6919008</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1801,12 +1801,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -2400,10 +2400,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120062695</v>
+        <v>120063666</v>
       </c>
       <c r="B17" t="n">
-        <v>97930</v>
+        <v>79131</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2412,45 +2412,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>503271</v>
+        <v>503181</v>
       </c>
       <c r="R17" t="n">
-        <v>6918864</v>
+        <v>6918937</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2479,7 +2475,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2489,7 +2485,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2504,12 +2500,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2628,10 +2624,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120063666</v>
+        <v>120062695</v>
       </c>
       <c r="B19" t="n">
-        <v>79131</v>
+        <v>97930</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2640,41 +2636,45 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>503181</v>
+        <v>503271</v>
       </c>
       <c r="R19" t="n">
-        <v>6918937</v>
+        <v>6918864</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2728,12 +2728,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 39496-2024 artfynd.xlsx
+++ b/artfynd/A 39496-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120063353</v>
+        <v>120063751</v>
       </c>
       <c r="B2" t="n">
-        <v>78279</v>
+        <v>97930</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>503182</v>
+        <v>503174</v>
       </c>
       <c r="R2" t="n">
-        <v>6918921</v>
+        <v>6918958</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120063290</v>
+        <v>120064431</v>
       </c>
       <c r="B3" t="n">
-        <v>90545</v>
+        <v>91858</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +812,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503218</v>
+        <v>503138</v>
       </c>
       <c r="R3" t="n">
-        <v>6918907</v>
+        <v>6919076</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -899,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120064431</v>
+        <v>120063666</v>
       </c>
       <c r="B4" t="n">
-        <v>91858</v>
+        <v>79131</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,41 +920,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503138</v>
+        <v>503181</v>
       </c>
       <c r="R4" t="n">
-        <v>6919076</v>
+        <v>6918937</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,19 +1008,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120064397</v>
+        <v>120063854</v>
       </c>
       <c r="B5" t="n">
         <v>97930</v>
@@ -1046,7 +1055,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1056,17 +1065,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503150</v>
+        <v>503171</v>
       </c>
       <c r="R5" t="n">
-        <v>6919090</v>
+        <v>6918993</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1095,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1114,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,22 +1129,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120063775</v>
+        <v>120064397</v>
       </c>
       <c r="B6" t="n">
-        <v>91858</v>
+        <v>97930</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,41 +1153,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503180</v>
+        <v>503150</v>
       </c>
       <c r="R6" t="n">
-        <v>6918964</v>
+        <v>6919090</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1207,7 +1225,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1235,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,22 +1250,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120064738</v>
+        <v>120062915</v>
       </c>
       <c r="B7" t="n">
-        <v>79659</v>
+        <v>91870</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,21 +1278,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>4366</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1284,13 +1302,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>503079</v>
+        <v>503303</v>
       </c>
       <c r="R7" t="n">
-        <v>6919159</v>
+        <v>6918868</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1319,7 +1337,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1329,7 +1347,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1344,19 +1362,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120064032</v>
+        <v>120064120</v>
       </c>
       <c r="B8" t="n">
         <v>97930</v>
@@ -1389,20 +1407,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>503163</v>
+        <v>503169</v>
       </c>
       <c r="R8" t="n">
-        <v>6919011</v>
+        <v>6919008</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1431,7 +1458,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1441,7 +1468,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1456,22 +1483,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120062610</v>
+        <v>120063775</v>
       </c>
       <c r="B9" t="n">
-        <v>78279</v>
+        <v>91858</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1480,41 +1507,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>503313</v>
+        <v>503180</v>
       </c>
       <c r="R9" t="n">
-        <v>6918866</v>
+        <v>6918964</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1543,7 +1570,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1553,7 +1580,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1568,22 +1595,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120064457</v>
+        <v>120062610</v>
       </c>
       <c r="B10" t="n">
-        <v>97930</v>
+        <v>78279</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1592,41 +1619,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>503135</v>
+        <v>503313</v>
       </c>
       <c r="R10" t="n">
-        <v>6919127</v>
+        <v>6918866</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1655,7 +1682,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1665,7 +1692,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1680,19 +1707,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120064120</v>
+        <v>120063873</v>
       </c>
       <c r="B11" t="n">
         <v>97930</v>
@@ -1727,7 +1754,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1741,10 +1768,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>503169</v>
+        <v>503181</v>
       </c>
       <c r="R11" t="n">
-        <v>6919008</v>
+        <v>6918946</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1776,7 +1803,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1786,7 +1813,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1813,10 +1840,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120064743</v>
+        <v>120062713</v>
       </c>
       <c r="B12" t="n">
-        <v>97930</v>
+        <v>57336</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1825,47 +1852,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>503071</v>
+        <v>503279</v>
       </c>
       <c r="R12" t="n">
-        <v>6919178</v>
+        <v>6918859</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1934,7 +1957,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120064281</v>
+        <v>120064743</v>
       </c>
       <c r="B13" t="n">
         <v>97930</v>
@@ -1969,7 +1992,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1983,10 +2006,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>503147</v>
+        <v>503071</v>
       </c>
       <c r="R13" t="n">
-        <v>6919079</v>
+        <v>6919178</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2055,10 +2078,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120063751</v>
+        <v>120064738</v>
       </c>
       <c r="B14" t="n">
-        <v>97930</v>
+        <v>79659</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2067,50 +2090,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>503174</v>
+        <v>503079</v>
       </c>
       <c r="R14" t="n">
-        <v>6918958</v>
+        <v>6919159</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2139,7 +2153,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2149,7 +2163,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2164,22 +2178,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120063670</v>
+        <v>120064366</v>
       </c>
       <c r="B15" t="n">
-        <v>78279</v>
+        <v>79623</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2192,21 +2206,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2216,10 +2230,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>503181</v>
+        <v>503147</v>
       </c>
       <c r="R15" t="n">
-        <v>6918937</v>
+        <v>6919083</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2251,7 +2265,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2261,7 +2275,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2288,10 +2302,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120062915</v>
+        <v>120064281</v>
       </c>
       <c r="B16" t="n">
-        <v>91870</v>
+        <v>97930</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2300,38 +2314,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>503303</v>
+        <v>503147</v>
       </c>
       <c r="R16" t="n">
-        <v>6918868</v>
+        <v>6919079</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2400,10 +2423,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120063666</v>
+        <v>120063353</v>
       </c>
       <c r="B17" t="n">
-        <v>79131</v>
+        <v>78279</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2416,37 +2439,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>503181</v>
+        <v>503182</v>
       </c>
       <c r="R17" t="n">
-        <v>6918937</v>
+        <v>6918921</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2475,7 +2498,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2485,7 +2508,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2500,22 +2523,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120064680</v>
+        <v>120062695</v>
       </c>
       <c r="B18" t="n">
-        <v>95478</v>
+        <v>97930</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2524,41 +2547,45 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>503081</v>
+        <v>503271</v>
       </c>
       <c r="R18" t="n">
-        <v>6919157</v>
+        <v>6918864</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2587,7 +2614,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2597,7 +2624,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2612,22 +2639,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120062695</v>
+        <v>120063670</v>
       </c>
       <c r="B19" t="n">
-        <v>97930</v>
+        <v>78279</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2636,45 +2663,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>503271</v>
+        <v>503181</v>
       </c>
       <c r="R19" t="n">
-        <v>6918864</v>
+        <v>6918937</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2703,7 +2726,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2713,7 +2736,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2728,22 +2751,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120062713</v>
+        <v>120064680</v>
       </c>
       <c r="B20" t="n">
-        <v>57336</v>
+        <v>95478</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2756,42 +2779,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>503279</v>
+        <v>503081</v>
       </c>
       <c r="R20" t="n">
-        <v>6918859</v>
+        <v>6919157</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2820,7 +2838,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2830,7 +2848,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2845,22 +2863,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120064366</v>
+        <v>120063290</v>
       </c>
       <c r="B21" t="n">
-        <v>79623</v>
+        <v>90545</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2869,25 +2887,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2897,13 +2915,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>503147</v>
+        <v>503218</v>
       </c>
       <c r="R21" t="n">
-        <v>6919083</v>
+        <v>6918907</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2932,7 +2950,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2942,7 +2960,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2957,19 +2975,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120063873</v>
+        <v>120064032</v>
       </c>
       <c r="B22" t="n">
         <v>97930</v>
@@ -3002,29 +3020,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503181</v>
+        <v>503163</v>
       </c>
       <c r="R22" t="n">
-        <v>6918946</v>
+        <v>6919011</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3053,7 +3062,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3063,7 +3072,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3078,19 +3087,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120063854</v>
+        <v>120064457</v>
       </c>
       <c r="B23" t="n">
         <v>97930</v>
@@ -3123,26 +3132,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>503171</v>
+        <v>503135</v>
       </c>
       <c r="R23" t="n">
-        <v>6918993</v>
+        <v>6919127</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 39496-2024 artfynd.xlsx
+++ b/artfynd/A 39496-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120063751</v>
+        <v>120063775</v>
       </c>
       <c r="B2" t="n">
-        <v>97930</v>
+        <v>91858</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>503174</v>
+        <v>503180</v>
       </c>
       <c r="R2" t="n">
-        <v>6918958</v>
+        <v>6918964</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -796,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120064431</v>
+        <v>120063670</v>
       </c>
       <c r="B3" t="n">
-        <v>91858</v>
+        <v>78279</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,41 +799,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503138</v>
+        <v>503181</v>
       </c>
       <c r="R3" t="n">
-        <v>6919076</v>
+        <v>6918937</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,22 +887,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120063666</v>
+        <v>120063873</v>
       </c>
       <c r="B4" t="n">
-        <v>79131</v>
+        <v>97930</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,28 +911,37 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Källmyran, Källmyran, Mpd</t>
@@ -951,7 +951,7 @@
         <v>503181</v>
       </c>
       <c r="R4" t="n">
-        <v>6918937</v>
+        <v>6918946</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -983,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,7 +1020,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120063854</v>
+        <v>120064032</v>
       </c>
       <c r="B5" t="n">
         <v>97930</v>
@@ -1053,26 +1053,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503171</v>
+        <v>503163</v>
       </c>
       <c r="R5" t="n">
-        <v>6918993</v>
+        <v>6919011</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1141,7 +1132,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120064397</v>
+        <v>120062695</v>
       </c>
       <c r="B6" t="n">
         <v>97930</v>
@@ -1176,12 +1167,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1190,13 +1176,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503150</v>
+        <v>503271</v>
       </c>
       <c r="R6" t="n">
-        <v>6919090</v>
+        <v>6918864</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1225,7 +1211,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1235,7 +1221,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,22 +1236,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120062915</v>
+        <v>120064738</v>
       </c>
       <c r="B7" t="n">
-        <v>91870</v>
+        <v>79659</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1278,21 +1264,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4366</v>
+        <v>6464</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1302,13 +1288,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>503303</v>
+        <v>503079</v>
       </c>
       <c r="R7" t="n">
-        <v>6918868</v>
+        <v>6919159</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1337,7 +1323,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1347,7 +1333,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,22 +1348,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120064120</v>
+        <v>120062610</v>
       </c>
       <c r="B8" t="n">
-        <v>97930</v>
+        <v>78279</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1386,47 +1372,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>503169</v>
+        <v>503313</v>
       </c>
       <c r="R8" t="n">
-        <v>6919008</v>
+        <v>6918866</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1458,7 +1435,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1468,7 +1445,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1495,10 +1472,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120063775</v>
+        <v>120064397</v>
       </c>
       <c r="B9" t="n">
-        <v>91858</v>
+        <v>97930</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1507,41 +1484,50 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>503180</v>
+        <v>503150</v>
       </c>
       <c r="R9" t="n">
-        <v>6918964</v>
+        <v>6919090</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1570,7 +1556,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1580,7 +1566,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1595,22 +1581,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120062610</v>
+        <v>120064457</v>
       </c>
       <c r="B10" t="n">
-        <v>78279</v>
+        <v>97930</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1619,41 +1605,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>503313</v>
+        <v>503135</v>
       </c>
       <c r="R10" t="n">
-        <v>6918866</v>
+        <v>6919127</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1682,7 +1668,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1692,7 +1678,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1707,22 +1693,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120063873</v>
+        <v>120063353</v>
       </c>
       <c r="B11" t="n">
-        <v>97930</v>
+        <v>78279</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1731,50 +1717,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>503181</v>
+        <v>503182</v>
       </c>
       <c r="R11" t="n">
-        <v>6918946</v>
+        <v>6918921</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1803,7 +1780,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1813,7 +1790,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1828,22 +1805,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120062713</v>
+        <v>120064743</v>
       </c>
       <c r="B12" t="n">
-        <v>57336</v>
+        <v>97930</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1852,43 +1829,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>503279</v>
+        <v>503071</v>
       </c>
       <c r="R12" t="n">
-        <v>6918859</v>
+        <v>6919178</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1957,7 +1938,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120064743</v>
+        <v>120064281</v>
       </c>
       <c r="B13" t="n">
         <v>97930</v>
@@ -1992,7 +1973,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2006,10 +1987,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>503071</v>
+        <v>503147</v>
       </c>
       <c r="R13" t="n">
-        <v>6919178</v>
+        <v>6919079</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2078,10 +2059,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120064738</v>
+        <v>120064431</v>
       </c>
       <c r="B14" t="n">
-        <v>79659</v>
+        <v>91858</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2094,37 +2075,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6464</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>503079</v>
+        <v>503138</v>
       </c>
       <c r="R14" t="n">
-        <v>6919159</v>
+        <v>6919076</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2153,7 +2134,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2163,7 +2144,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2178,22 +2159,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120064366</v>
+        <v>120064120</v>
       </c>
       <c r="B15" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2202,38 +2183,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>503147</v>
+        <v>503169</v>
       </c>
       <c r="R15" t="n">
-        <v>6919083</v>
+        <v>6919008</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2265,7 +2255,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2275,7 +2265,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2302,7 +2292,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120064281</v>
+        <v>120063751</v>
       </c>
       <c r="B16" t="n">
         <v>97930</v>
@@ -2337,7 +2327,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2351,10 +2341,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>503147</v>
+        <v>503174</v>
       </c>
       <c r="R16" t="n">
-        <v>6919079</v>
+        <v>6918958</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2423,10 +2413,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120063353</v>
+        <v>120062915</v>
       </c>
       <c r="B17" t="n">
-        <v>78279</v>
+        <v>91870</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2435,38 +2425,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>4366</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>503182</v>
+        <v>503303</v>
       </c>
       <c r="R17" t="n">
-        <v>6918921</v>
+        <v>6918868</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2535,10 +2525,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120062695</v>
+        <v>120064366</v>
       </c>
       <c r="B18" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2547,45 +2537,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>503271</v>
+        <v>503147</v>
       </c>
       <c r="R18" t="n">
-        <v>6918864</v>
+        <v>6919083</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2614,7 +2600,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2624,7 +2610,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2639,22 +2625,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120063670</v>
+        <v>120064680</v>
       </c>
       <c r="B19" t="n">
-        <v>78279</v>
+        <v>95478</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2667,21 +2653,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>53</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2691,10 +2677,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>503181</v>
+        <v>503081</v>
       </c>
       <c r="R19" t="n">
-        <v>6918937</v>
+        <v>6919157</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2726,7 +2712,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2736,7 +2722,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2763,10 +2749,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120064680</v>
+        <v>120062713</v>
       </c>
       <c r="B20" t="n">
-        <v>95478</v>
+        <v>57336</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2779,37 +2765,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>503081</v>
+        <v>503279</v>
       </c>
       <c r="R20" t="n">
-        <v>6919157</v>
+        <v>6918859</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2838,7 +2829,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2848,7 +2839,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2863,12 +2854,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2987,7 +2978,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120064032</v>
+        <v>120063854</v>
       </c>
       <c r="B22" t="n">
         <v>97930</v>
@@ -3020,17 +3011,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503163</v>
+        <v>503171</v>
       </c>
       <c r="R22" t="n">
-        <v>6919011</v>
+        <v>6918993</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3099,10 +3099,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120064457</v>
+        <v>120063666</v>
       </c>
       <c r="B23" t="n">
-        <v>97930</v>
+        <v>79131</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3111,41 +3111,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>503135</v>
+        <v>503181</v>
       </c>
       <c r="R23" t="n">
-        <v>6919127</v>
+        <v>6918937</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3199,12 +3199,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 39496-2024 artfynd.xlsx
+++ b/artfynd/A 39496-2024 artfynd.xlsx
@@ -1472,10 +1472,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120064397</v>
+        <v>120063353</v>
       </c>
       <c r="B9" t="n">
-        <v>97930</v>
+        <v>78279</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1484,50 +1484,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>503150</v>
+        <v>503182</v>
       </c>
       <c r="R9" t="n">
-        <v>6919090</v>
+        <v>6918921</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1556,7 +1547,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1566,7 +1557,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,19 +1572,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120064457</v>
+        <v>120064397</v>
       </c>
       <c r="B10" t="n">
         <v>97930</v>
@@ -1626,20 +1617,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>503135</v>
+        <v>503150</v>
       </c>
       <c r="R10" t="n">
-        <v>6919127</v>
+        <v>6919090</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,22 +1693,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120063353</v>
+        <v>120064457</v>
       </c>
       <c r="B11" t="n">
-        <v>78279</v>
+        <v>97930</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1717,25 +1717,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>503182</v>
+        <v>503135</v>
       </c>
       <c r="R11" t="n">
-        <v>6918921</v>
+        <v>6919127</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2059,10 +2059,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120064431</v>
+        <v>120064120</v>
       </c>
       <c r="B14" t="n">
-        <v>91858</v>
+        <v>97930</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2071,41 +2071,50 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
+          <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>503138</v>
+        <v>503169</v>
       </c>
       <c r="R14" t="n">
-        <v>6919076</v>
+        <v>6919008</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2134,7 +2143,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2144,7 +2153,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2159,22 +2168,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120064120</v>
+        <v>120064431</v>
       </c>
       <c r="B15" t="n">
-        <v>97930</v>
+        <v>91858</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2183,50 +2192,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Källmyran, Källmyran, Mpd</t>
+          <t>Hälltjärnen, Hälltjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>503169</v>
+        <v>503138</v>
       </c>
       <c r="R15" t="n">
-        <v>6919008</v>
+        <v>6919076</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2280,12 +2280,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 39496-2024 artfynd.xlsx
+++ b/artfynd/A 39496-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120064680</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120062394</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120063775</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120064431</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120062915</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120063290</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120064366</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120064738</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1640,6 +1685,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120062713</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1751,6 +1801,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120062695</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1867,6 +1922,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120063751</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1983,6 +2043,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120063854</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2099,6 +2164,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120063873</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2206,6 +2276,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120064032</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2322,6 +2397,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120064120</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2438,6 +2518,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120064281</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2554,6 +2639,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120064397</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2661,6 +2751,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120064457</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2777,6 +2872,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120064743</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2884,6 +2984,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120062610</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2991,6 +3096,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120063353</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3098,6 +3208,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120063670</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3205,8 +3320,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120063666</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>